--- a/public/downloads/WerghiDynamic2024.xlsx
+++ b/public/downloads/WerghiDynamic2024.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="53">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>CH3</t>
@@ -653,10 +676,10 @@
         <v>682</v>
       </c>
       <c r="N3" s="5">
-        <v>1761.81134724617</v>
+        <v>1761811.34724617</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03336195245594823</v>
+        <v>33.36195245594823</v>
       </c>
       <c r="P3" s="5">
         <v>52809</v>
@@ -703,10 +726,10 @@
         <v>682</v>
       </c>
       <c r="N4" s="5">
-        <v>4328.444574117661</v>
+        <v>4328444.574117661</v>
       </c>
       <c r="O4" s="4">
-        <v>0.06519134547439094</v>
+        <v>65.19134547439094</v>
       </c>
       <c r="P4" s="5">
         <v>66396</v>
@@ -753,10 +776,10 @@
         <v>682</v>
       </c>
       <c r="N5" s="5">
-        <v>7727.356581687927</v>
+        <v>7727356.581687927</v>
       </c>
       <c r="O5" s="4">
-        <v>0.135401376935131</v>
+        <v>135.401376935131</v>
       </c>
       <c r="P5" s="5">
         <v>57070</v>
@@ -803,10 +826,10 @@
         <v>682</v>
       </c>
       <c r="N6" s="5">
-        <v>5474.107809066772</v>
+        <v>5474107.809066772</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08778939634458781</v>
+        <v>87.78939634458781</v>
       </c>
       <c r="P6" s="5">
         <v>62355</v>
@@ -853,10 +876,10 @@
         <v>682</v>
       </c>
       <c r="N7" s="5">
-        <v>12034.74124550819</v>
+        <v>12034741.24550819</v>
       </c>
       <c r="O7" s="4">
-        <v>0.250270161280766</v>
+        <v>250.270161280766</v>
       </c>
       <c r="P7" s="5">
         <v>48087</v>
@@ -903,10 +926,10 @@
         <v>682</v>
       </c>
       <c r="N8" s="5">
-        <v>973.7000379562378</v>
+        <v>973700.0379562378</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01820953093125819</v>
+        <v>18.20953093125819</v>
       </c>
       <c r="P8" s="5">
         <v>53472</v>
@@ -953,10 +976,10 @@
         <v>682</v>
       </c>
       <c r="N9" s="5">
-        <v>1937.417086601257</v>
+        <v>1937417.086601257</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03134218371918236</v>
+        <v>31.34218371918235</v>
       </c>
       <c r="P9" s="5">
         <v>61815</v>
@@ -1003,10 +1026,10 @@
         <v>682</v>
       </c>
       <c r="N10" s="5">
-        <v>4975.082573413849</v>
+        <v>4975082.573413849</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08513874515981601</v>
+        <v>85.13874515981601</v>
       </c>
       <c r="P10" s="5">
         <v>58435</v>
@@ -1053,10 +1076,10 @@
         <v>682</v>
       </c>
       <c r="N11" s="5">
-        <v>2450.830444574356</v>
+        <v>2450830.444574356</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04247392541981831</v>
+        <v>42.47392541981831</v>
       </c>
       <c r="P11" s="5">
         <v>57702</v>
@@ -1103,10 +1126,10 @@
         <v>682</v>
       </c>
       <c r="N12" s="5">
-        <v>1344.236167907715</v>
+        <v>1344236.167907715</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02165607951907003</v>
+        <v>21.65607951907003</v>
       </c>
       <c r="P12" s="5">
         <v>62072</v>
@@ -1153,10 +1176,10 @@
         <v>682</v>
       </c>
       <c r="N13" s="5">
-        <v>4044.541590452194</v>
+        <v>4044541.590452194</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07643613392395575</v>
+        <v>76.43613392395575</v>
       </c>
       <c r="P13" s="5">
         <v>52914</v>
@@ -1203,10 +1226,10 @@
         <v>24</v>
       </c>
       <c r="N14" s="5">
-        <v>295.259073972702</v>
+        <v>295259.073972702</v>
       </c>
       <c r="O14" s="4">
-        <v>0.228883003079614</v>
+        <v>228.883003079614</v>
       </c>
       <c r="P14" s="5">
         <v>1290</v>
@@ -1253,10 +1276,10 @@
         <v>24</v>
       </c>
       <c r="N15" s="5">
-        <v>444.8561878204346</v>
+        <v>444856.1878204346</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2253577445898858</v>
+        <v>225.3577445898858</v>
       </c>
       <c r="P15" s="5">
         <v>1974</v>
@@ -1303,10 +1326,10 @@
         <v>24</v>
       </c>
       <c r="N16" s="5">
-        <v>116.5299167633057</v>
+        <v>116529.9167633057</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1011544416348139</v>
+        <v>101.1544416348139</v>
       </c>
       <c r="P16" s="5">
         <v>1152</v>
@@ -1353,10 +1376,10 @@
         <v>24</v>
       </c>
       <c r="N17" s="5">
-        <v>230.5340480804443</v>
+        <v>230534.0480804443</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1027335330126757</v>
+        <v>102.7335330126757</v>
       </c>
       <c r="P17" s="5">
         <v>2244</v>
@@ -1384,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1395,9 +1418,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1431,8 +1460,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1454,25 +1491,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1248462585706201</v>
+        <v>0.4267325092927209</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1248462585706201</v>
+        <v>0.4267325092927209</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1442367595427429</v>
+        <v>0.4194978875456257</v>
       </c>
       <c r="E3" s="4">
-        <v>88.14625850340134</v>
+        <v>92.36394557823131</v>
       </c>
       <c r="F3" s="4">
-        <v>91.26957494407152</v>
+        <v>93.74161073825523</v>
       </c>
       <c r="G3" s="5">
         <v>24</v>
@@ -1495,9 +1550,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.4267325092927209</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.03041699886445727</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03041699886445727</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1508,6 +1581,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1515,7 +1589,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1526,9 +1600,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1562,8 +1642,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1585,34 +1673,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.08443622994323736</v>
+        <v>0.1686828398042254</v>
       </c>
       <c r="C3" s="4">
-        <v>0.08443622994323736</v>
+        <v>0.10983535040641</v>
       </c>
       <c r="D3" s="4">
-        <v>0.0691376654473892</v>
+        <v>0.08774726711344154</v>
       </c>
       <c r="E3" s="4">
-        <v>92.17687074829931</v>
+        <v>82.70975056689352</v>
       </c>
       <c r="F3" s="4">
-        <v>92.52796420581657</v>
+        <v>78.27647278150792</v>
       </c>
       <c r="G3" s="5">
         <v>24</v>
       </c>
       <c r="H3" s="5">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -1626,9 +1732,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.10983535040641</v>
+      </c>
+      <c r="O3" s="5">
+        <v>16</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1023285900439449</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06083104712158161</v>
+      </c>
+      <c r="R3" s="5">
+        <v>16</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1639,6 +1763,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1646,7 +1771,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1657,9 +1782,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1693,8 +1824,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1716,25 +1855,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.06085269903727308</v>
+        <v>0.1248462585706201</v>
       </c>
       <c r="C3" s="4">
-        <v>0.06085269903727308</v>
+        <v>0.1248462585706201</v>
       </c>
       <c r="D3" s="4">
-        <v>0.06036989843973828</v>
+        <v>0.1442367595427429</v>
       </c>
       <c r="E3" s="4">
-        <v>88.42261904761905</v>
+        <v>88.14625850340134</v>
       </c>
       <c r="F3" s="4">
-        <v>92.43754660700969</v>
+        <v>91.26957494407152</v>
       </c>
       <c r="G3" s="5">
         <v>24</v>
@@ -1757,9 +1914,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>0.1248462585706201</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.03969891344500378</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03969891344500378</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1770,6 +1945,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1777,7 +1953,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1788,9 +1964,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1824,8 +2006,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1847,25 +2037,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1858336591058306</v>
+        <v>0.08443622994323736</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1858336591058306</v>
+        <v>0.08443622994323736</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1887444320652219</v>
+        <v>0.0691376654473892</v>
       </c>
       <c r="E3" s="4">
-        <v>93.94557823129252</v>
+        <v>92.17687074829931</v>
       </c>
       <c r="F3" s="4">
-        <v>95.1398210290828</v>
+        <v>92.52796420581657</v>
       </c>
       <c r="G3" s="5">
         <v>24</v>
@@ -1888,9 +2096,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.04170438283019588</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08443622994323736</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08443622994323736</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1901,6 +2127,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1908,7 +2135,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1919,9 +2146,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1955,8 +2188,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1978,25 +2219,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2491317576832651</v>
+        <v>0.06085269903727308</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2491317576832651</v>
+        <v>0.06085269903727308</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2526873336898341</v>
+        <v>0.06036989843973828</v>
       </c>
       <c r="E3" s="4">
-        <v>98.13775510204081</v>
+        <v>88.42261904761905</v>
       </c>
       <c r="F3" s="4">
-        <v>97.98657718120805</v>
+        <v>92.43754660700969</v>
       </c>
       <c r="G3" s="5">
         <v>24</v>
@@ -2019,9 +2278,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>0.0007098055548138879</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06094266193888388</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06094266193888388</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2032,6 +2309,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2039,7 +2317,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2050,9 +2328,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2086,8 +2370,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2109,25 +2401,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.0553882660850927</v>
+        <v>0.1858336591058306</v>
       </c>
       <c r="C3" s="4">
-        <v>0.0553882660850927</v>
+        <v>0.1858336591058306</v>
       </c>
       <c r="D3" s="4">
-        <v>0.05347100445479717</v>
+        <v>0.1887444320652219</v>
       </c>
       <c r="E3" s="4">
-        <v>91.48809523809526</v>
+        <v>93.94557823129252</v>
       </c>
       <c r="F3" s="4">
-        <v>94.13870246085011</v>
+        <v>95.1398210290828</v>
       </c>
       <c r="G3" s="5">
         <v>24</v>
@@ -2150,9 +2460,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.1858336591058306</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.02576689583953634</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.02576689583953634</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2163,6 +2491,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2170,7 +2499,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2181,9 +2510,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2217,8 +2552,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2240,25 +2583,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2627271946933885</v>
+        <v>0.2491317576832651</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2627271946933885</v>
+        <v>0.2491317576832651</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2648856874969632</v>
+        <v>0.2526873336898341</v>
       </c>
       <c r="E3" s="4">
-        <v>98.41836734693878</v>
+        <v>98.13775510204081</v>
       </c>
       <c r="F3" s="4">
-        <v>98.30536912751678</v>
+        <v>97.98657718120805</v>
       </c>
       <c r="G3" s="5">
         <v>24</v>
@@ -2281,9 +2642,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>0.2491317576832651</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.01986255870956897</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.01986255870956897</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2294,6 +2673,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2301,7 +2681,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2312,9 +2692,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2348,8 +2734,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2371,25 +2765,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6245080691245107</v>
+        <v>0.0553882660850927</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6245080691245107</v>
+        <v>0.0553882660850927</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6413096623288453</v>
+        <v>0.05347100445479717</v>
       </c>
       <c r="E3" s="4">
-        <v>88.8095238095238</v>
+        <v>91.48809523809526</v>
       </c>
       <c r="F3" s="4">
-        <v>92.49207680835197</v>
+        <v>94.13870246085011</v>
       </c>
       <c r="G3" s="5">
         <v>24</v>
@@ -2412,9 +2824,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.05279193826845555</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.02923115799377069</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.02923115799377069</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2425,12 +2855,1234 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2627271946933885</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2627271946933885</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2648856874969632</v>
+      </c>
+      <c r="E3" s="4">
+        <v>98.41836734693878</v>
+      </c>
+      <c r="F3" s="4">
+        <v>98.30536912751678</v>
+      </c>
+      <c r="G3" s="5">
+        <v>24</v>
+      </c>
+      <c r="H3" s="5">
+        <v>24</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.2627271946933885</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.01802876236818553</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.01802876236818553</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.6245080691245107</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.6245080691245107</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6413096623288453</v>
+      </c>
+      <c r="E3" s="4">
+        <v>88.8095238095238</v>
+      </c>
+      <c r="F3" s="4">
+        <v>92.49207680835197</v>
+      </c>
+      <c r="G3" s="5">
+        <v>24</v>
+      </c>
+      <c r="H3" s="5">
+        <v>24</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.6245080691245107</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.03581291190950923</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03581291190950923</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>92.66862170087975</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>7.331378299120235</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>7.331378299120235</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.4515525013192363</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3153245102654286</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.472119793129487</v>
+      </c>
+      <c r="K3" s="4">
+        <v>81.51674746144793</v>
+      </c>
+      <c r="L3" s="4">
+        <v>88.20897872424173</v>
+      </c>
+      <c r="M3" s="5">
+        <v>682</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1761811.34724617</v>
+      </c>
+      <c r="O3" s="4">
+        <v>33.36195245594823</v>
+      </c>
+      <c r="P3" s="5">
+        <v>52809</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>92.66862170087975</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>7.331378299120235</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>7.331378299120235</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.4998944448784994</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3695803999410585</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.5044599374091835</v>
+      </c>
+      <c r="K4" s="4">
+        <v>82.38559059987632</v>
+      </c>
+      <c r="L4" s="4">
+        <v>87.99353132975126</v>
+      </c>
+      <c r="M4" s="5">
+        <v>682</v>
+      </c>
+      <c r="N4" s="5">
+        <v>4328444.574117661</v>
+      </c>
+      <c r="O4" s="4">
+        <v>65.19134547439094</v>
+      </c>
+      <c r="P4" s="5">
+        <v>66396</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>92.66862170087975</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>7.331378299120235</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>7.331378299120235</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.4262523392158525</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2915622546026473</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.4284796080942141</v>
+      </c>
+      <c r="K5" s="4">
+        <v>81.33490933030104</v>
+      </c>
+      <c r="L5" s="4">
+        <v>89.25080530352233</v>
+      </c>
+      <c r="M5" s="5">
+        <v>682</v>
+      </c>
+      <c r="N5" s="5">
+        <v>7727356.581687927</v>
+      </c>
+      <c r="O5" s="4">
+        <v>135.401376935131</v>
+      </c>
+      <c r="P5" s="5">
+        <v>57070</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>86.80351906158357</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1.759530791788857</v>
+      </c>
+      <c r="D6" s="3">
+        <v>11.43695014662756</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>4.398826979472141</v>
+      </c>
+      <c r="G6" s="3">
+        <v>7.038123167155426</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.4893256126657757</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3566814967160137</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.4944362746668108</v>
+      </c>
+      <c r="K6" s="4">
+        <v>80.69154347956174</v>
+      </c>
+      <c r="L6" s="4">
+        <v>86.48162727075912</v>
+      </c>
+      <c r="M6" s="5">
+        <v>682</v>
+      </c>
+      <c r="N6" s="5">
+        <v>5474107.809066772</v>
+      </c>
+      <c r="O6" s="4">
+        <v>87.78939634458781</v>
+      </c>
+      <c r="P6" s="5">
+        <v>62355</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>92.66862170087975</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>7.331378299120235</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>7.331378299120235</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.4266701888698711</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.2907669854804272</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.4292581090807714</v>
+      </c>
+      <c r="K7" s="4">
+        <v>86.24399026472759</v>
+      </c>
+      <c r="L7" s="4">
+        <v>90.434962309827</v>
+      </c>
+      <c r="M7" s="5">
+        <v>682</v>
+      </c>
+      <c r="N7" s="5">
+        <v>12034741.24550819</v>
+      </c>
+      <c r="O7" s="4">
+        <v>250.270161280766</v>
+      </c>
+      <c r="P7" s="5">
+        <v>48087</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>92.66862170087975</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7.331378299120235</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>7.331378299120235</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.4375876579741023</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.3017091198327465</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.4432067398297294</v>
+      </c>
+      <c r="K8" s="4">
+        <v>84.00472799090309</v>
+      </c>
+      <c r="L8" s="4">
+        <v>89.70664646027245</v>
+      </c>
+      <c r="M8" s="5">
+        <v>682</v>
+      </c>
+      <c r="N8" s="5">
+        <v>973700.0379562378</v>
+      </c>
+      <c r="O8" s="4">
+        <v>18.20953093125819</v>
+      </c>
+      <c r="P8" s="5">
+        <v>53472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>90.32258064516128</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1.466275659824047</v>
+      </c>
+      <c r="D9" s="3">
+        <v>8.211143695014663</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1.173020527859238</v>
+      </c>
+      <c r="G9" s="3">
+        <v>7.038123167155426</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.4876395462411636</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.364293326952278</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.5110701234840219</v>
+      </c>
+      <c r="K9" s="4">
+        <v>85.06767809763133</v>
+      </c>
+      <c r="L9" s="4">
+        <v>87.76668503611573</v>
+      </c>
+      <c r="M9" s="5">
+        <v>682</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1937417.086601257</v>
+      </c>
+      <c r="O9" s="4">
+        <v>31.34218371918235</v>
+      </c>
+      <c r="P9" s="5">
+        <v>61815</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>91.49560117302052</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>8.504398826979472</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1.173020527859238</v>
+      </c>
+      <c r="G10" s="3">
+        <v>7.331378299120235</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.5168902861511234</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.3934574019363399</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.5231162408413157</v>
+      </c>
+      <c r="K10" s="4">
+        <v>82.06680032716902</v>
+      </c>
+      <c r="L10" s="4">
+        <v>87.29567268266122</v>
+      </c>
+      <c r="M10" s="5">
+        <v>682</v>
+      </c>
+      <c r="N10" s="5">
+        <v>4975082.573413849</v>
+      </c>
+      <c r="O10" s="4">
+        <v>85.13874515981601</v>
+      </c>
+      <c r="P10" s="5">
+        <v>58435</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>92.66862170087975</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>7.331378299120235</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>7.331378299120235</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.4622794895000493</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.3272888751742891</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.4703828895980458</v>
+      </c>
+      <c r="K11" s="4">
+        <v>84.01629860155205</v>
+      </c>
+      <c r="L11" s="4">
+        <v>89.26779704383075</v>
+      </c>
+      <c r="M11" s="5">
+        <v>682</v>
+      </c>
+      <c r="N11" s="5">
+        <v>2450830.444574356</v>
+      </c>
+      <c r="O11" s="4">
+        <v>42.47392541981831</v>
+      </c>
+      <c r="P11" s="5">
+        <v>57702</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>92.81524926686217</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>7.184750733137831</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>7.184750733137831</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.4578420204313769</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.3272002887336231</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.4652216236335473</v>
+      </c>
+      <c r="K12" s="4">
+        <v>82.26270273505295</v>
+      </c>
+      <c r="L12" s="4">
+        <v>88.48893240698825</v>
+      </c>
+      <c r="M12" s="5">
+        <v>682</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1344236.167907715</v>
+      </c>
+      <c r="O12" s="4">
+        <v>21.65607951907003</v>
+      </c>
+      <c r="P12" s="5">
+        <v>62072</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>92.66862170087975</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>7.331378299120235</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>7.331378299120235</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.427220555601768</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.2902324719933548</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.435056077242237</v>
+      </c>
+      <c r="K13" s="4">
+        <v>82.9750433897899</v>
+      </c>
+      <c r="L13" s="4">
+        <v>89.14977333412057</v>
+      </c>
+      <c r="M13" s="5">
+        <v>682</v>
+      </c>
+      <c r="N13" s="5">
+        <v>4044541.590452194</v>
+      </c>
+      <c r="O13" s="4">
+        <v>76.43613392395575</v>
+      </c>
+      <c r="P13" s="5">
+        <v>52914</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>100</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.01986255870956897</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.01986255870956897</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.01949918339171959</v>
+      </c>
+      <c r="K14" s="4">
+        <v>98.13775510204081</v>
+      </c>
+      <c r="L14" s="4">
+        <v>97.98657718120805</v>
+      </c>
+      <c r="M14" s="5">
+        <v>24</v>
+      </c>
+      <c r="N14" s="5">
+        <v>295259.073972702</v>
+      </c>
+      <c r="O14" s="4">
+        <v>228.883003079614</v>
+      </c>
+      <c r="P14" s="5">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>100</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.02923115799377069</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.02923115799377069</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.03117607444244576</v>
+      </c>
+      <c r="K15" s="4">
+        <v>91.48809523809526</v>
+      </c>
+      <c r="L15" s="4">
+        <v>94.13870246085011</v>
+      </c>
+      <c r="M15" s="5">
+        <v>24</v>
+      </c>
+      <c r="N15" s="5">
+        <v>444856.1878204346</v>
+      </c>
+      <c r="O15" s="4">
+        <v>225.3577445898858</v>
+      </c>
+      <c r="P15" s="5">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>100</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.01802876236818553</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.01802876236818553</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.01874862504782006</v>
+      </c>
+      <c r="K16" s="4">
+        <v>98.41836734693878</v>
+      </c>
+      <c r="L16" s="4">
+        <v>98.30536912751678</v>
+      </c>
+      <c r="M16" s="5">
+        <v>24</v>
+      </c>
+      <c r="N16" s="5">
+        <v>116529.9167633057</v>
+      </c>
+      <c r="O16" s="4">
+        <v>101.1544416348139</v>
+      </c>
+      <c r="P16" s="5">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.03581291190950923</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.03581291190950923</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.04048272202358524</v>
+      </c>
+      <c r="K17" s="4">
+        <v>88.8095238095238</v>
+      </c>
+      <c r="L17" s="4">
+        <v>92.49207680835197</v>
+      </c>
+      <c r="M17" s="5">
+        <v>24</v>
+      </c>
+      <c r="N17" s="5">
+        <v>230534.0480804443</v>
+      </c>
+      <c r="O17" s="4">
+        <v>102.7335330126757</v>
+      </c>
+      <c r="P17" s="5">
+        <v>2244</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3185,9 +4837,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>632</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>50</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>50</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>632</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>50</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>50</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>632</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>50</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>50</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>592</v>
+      </c>
+      <c r="C6" s="5">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5">
+        <v>78</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>30</v>
+      </c>
+      <c r="G6" s="5">
+        <v>48</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>14</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>632</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>50</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>50</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>632</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>50</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>50</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>616</v>
+      </c>
+      <c r="C9" s="5">
+        <v>10</v>
+      </c>
+      <c r="D9" s="5">
+        <v>56</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>8</v>
+      </c>
+      <c r="G9" s="5">
+        <v>48</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>6</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>624</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>58</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>8</v>
+      </c>
+      <c r="G10" s="5">
+        <v>50</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>632</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>50</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>50</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>633</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>49</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>49</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>632</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>50</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>50</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>24</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>24</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>24</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>24</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3198,9 +5605,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3234,8 +5647,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3257,10 +5678,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2491550111108355</v>
@@ -3298,9 +5737,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.2491550111108355</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09153112491536536</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09153112491536536</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3311,14 +5768,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3329,9 +5787,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3365,8 +5829,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3388,10 +5860,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3462827963961495</v>
@@ -3429,9 +5919,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.3462827963961495</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.03145374389406778</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03145374389406778</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3442,14 +5950,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3460,9 +5969,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3496,8 +6011,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3519,10 +6042,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.08044836987785094</v>
@@ -3560,9 +6101,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.07765869152628706</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.03985813784775378</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03985813784775378</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3573,14 +6132,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3591,9 +6151,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3627,8 +6193,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3650,10 +6224,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.1717206302616331</v>
@@ -3691,9 +6283,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.1809437421223123</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06949339269271088</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.07232433699843796</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3704,14 +6314,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3722,9 +6333,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3758,8 +6375,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3781,10 +6406,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.1223952309952843</v>
@@ -3822,9 +6465,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>0.1223952309952843</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.01543094200710667</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.01543094200710667</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3835,268 +6496,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4267325092927209</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4267325092927209</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4194978875456257</v>
-      </c>
-      <c r="E3" s="4">
-        <v>92.36394557823131</v>
-      </c>
-      <c r="F3" s="4">
-        <v>93.74161073825523</v>
-      </c>
-      <c r="G3" s="5">
-        <v>24</v>
-      </c>
-      <c r="H3" s="5">
-        <v>24</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.1686828398042254</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.10983535040641</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.08774726711344154</v>
-      </c>
-      <c r="E3" s="4">
-        <v>82.70975056689352</v>
-      </c>
-      <c r="F3" s="4">
-        <v>78.27647278150792</v>
-      </c>
-      <c r="G3" s="5">
-        <v>24</v>
-      </c>
-      <c r="H3" s="5">
-        <v>16</v>
-      </c>
-      <c r="I3" s="5">
-        <v>8</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/WerghiDynamic2024.xlsx
+++ b/public/downloads/WerghiDynamic2024.xlsx
@@ -1551,16 +1551,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4267325092927209</v>
+        <v>-0.4302139601296773</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.03041699886445727</v>
+        <v>0.03012517721612299</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.03041699886445727</v>
+        <v>0.03012517721612299</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -1733,13 +1733,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.10983535040641</v>
+        <v>-0.1010994139120456</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1023285900439449</v>
+        <v>0.1036379045052603</v>
       </c>
       <c r="Q3" s="4">
         <v>0.06083104712158161</v>
@@ -1915,16 +1915,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1248462585706201</v>
+        <v>0.128353267054278</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.03969891344500378</v>
+        <v>0.03916798795753688</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.03969891344500378</v>
+        <v>0.03916798795753688</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -2097,7 +2097,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.04170438283019588</v>
+        <v>-0.02094204843261593</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
@@ -2279,16 +2279,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.0007098055548138879</v>
+        <v>-0.003061942128290696</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06094266193888388</v>
+        <v>0.06085269903727308</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06094266193888388</v>
+        <v>0.06085269903727308</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -2461,16 +2461,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1858336591058306</v>
+        <v>-0.1926225026257313</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.02576689583953634</v>
+        <v>0.02541718371642669</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.02576689583953634</v>
+        <v>0.02541718371642669</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -2643,7 +2643,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2491317576832651</v>
+        <v>0.2477538428891182</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
@@ -2825,16 +2825,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.05279193826845555</v>
+        <v>-0.0612239063190998</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.02923115799377069</v>
+        <v>0.02712473190922804</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.02923115799377069</v>
+        <v>0.02712473190922804</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -3007,16 +3007,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2627271946933885</v>
+        <v>0.2671175331726803</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.01802876236818553</v>
+        <v>0.01766552409120202</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.01802876236818553</v>
+        <v>0.01766552409120202</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -3189,16 +3189,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.6245080691245107</v>
+        <v>0.6159814811223931</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.03581291190950923</v>
+        <v>0.03366057925779872</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.03581291190950923</v>
+        <v>0.03366057925779872</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -3335,13 +3335,13 @@
         <v>7.331378299120235</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4515525013192363</v>
+        <v>0.3628442173580711</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3153245102654286</v>
+        <v>0.175505543168143</v>
       </c>
       <c r="J3" s="4">
-        <v>0.472119793129487</v>
+        <v>0.3808342251148131</v>
       </c>
       <c r="K3" s="4">
         <v>81.51674746144793</v>
@@ -3385,13 +3385,13 @@
         <v>7.331378299120235</v>
       </c>
       <c r="H4" s="4">
-        <v>0.4998944448784994</v>
+        <v>0.4386303761996111</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3695803999410585</v>
+        <v>0.2587912557124588</v>
       </c>
       <c r="J4" s="4">
-        <v>0.5044599374091835</v>
+        <v>0.439257434420232</v>
       </c>
       <c r="K4" s="4">
         <v>82.38559059987632</v>
@@ -3435,13 +3435,13 @@
         <v>7.331378299120235</v>
       </c>
       <c r="H5" s="4">
-        <v>0.4262523392158525</v>
+        <v>0.336461529096249</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2915622546026473</v>
+        <v>0.1492706130214037</v>
       </c>
       <c r="J5" s="4">
-        <v>0.4284796080942141</v>
+        <v>0.3355386276762652</v>
       </c>
       <c r="K5" s="4">
         <v>81.33490933030104</v>
@@ -3467,13 +3467,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>86.80351906158357</v>
+        <v>86.51026392961877</v>
       </c>
       <c r="C6" s="3">
         <v>1.759530791788857</v>
       </c>
       <c r="D6" s="3">
-        <v>11.43695014662756</v>
+        <v>11.73020527859238</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
@@ -3482,16 +3482,16 @@
         <v>4.398826979472141</v>
       </c>
       <c r="G6" s="3">
-        <v>7.038123167155426</v>
+        <v>7.331378299120235</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4893256126657757</v>
+        <v>0.3927864770992392</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3566814967160137</v>
+        <v>0.1981259349412748</v>
       </c>
       <c r="J6" s="4">
-        <v>0.4944362746668108</v>
+        <v>0.3970222719301301</v>
       </c>
       <c r="K6" s="4">
         <v>80.69154347956174</v>
@@ -3535,13 +3535,13 @@
         <v>7.331378299120235</v>
       </c>
       <c r="H7" s="4">
-        <v>0.4266701888698711</v>
+        <v>0.3368009397164834</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2907669854804272</v>
+        <v>0.1490578743727139</v>
       </c>
       <c r="J7" s="4">
-        <v>0.4292581090807714</v>
+        <v>0.3301215083218034</v>
       </c>
       <c r="K7" s="4">
         <v>86.24399026472759</v>
@@ -3585,13 +3585,13 @@
         <v>7.331378299120235</v>
       </c>
       <c r="H8" s="4">
-        <v>0.4375876579741023</v>
+        <v>0.3500434246008935</v>
       </c>
       <c r="I8" s="4">
-        <v>0.3017091198327465</v>
+        <v>0.1636319072780881</v>
       </c>
       <c r="J8" s="4">
-        <v>0.4432067398297294</v>
+        <v>0.3447642114789519</v>
       </c>
       <c r="K8" s="4">
         <v>84.00472799090309</v>
@@ -3617,13 +3617,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>90.32258064516128</v>
+        <v>90.02932551319648</v>
       </c>
       <c r="C9" s="3">
         <v>1.466275659824047</v>
       </c>
       <c r="D9" s="3">
-        <v>8.211143695014663</v>
+        <v>8.504398826979472</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -3632,16 +3632,16 @@
         <v>1.173020527859238</v>
       </c>
       <c r="G9" s="3">
-        <v>7.038123167155426</v>
+        <v>7.331378299120235</v>
       </c>
       <c r="H9" s="4">
-        <v>0.4876395462411636</v>
+        <v>0.4013437335474157</v>
       </c>
       <c r="I9" s="4">
-        <v>0.364293326952278</v>
+        <v>0.214385374391159</v>
       </c>
       <c r="J9" s="4">
-        <v>0.5110701234840219</v>
+        <v>0.4150673661238737</v>
       </c>
       <c r="K9" s="4">
         <v>85.06767809763133</v>
@@ -3685,13 +3685,13 @@
         <v>7.331378299120235</v>
       </c>
       <c r="H10" s="4">
-        <v>0.5168902861511234</v>
+        <v>0.4446583727178829</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3934574019363399</v>
+        <v>0.266944891703869</v>
       </c>
       <c r="J10" s="4">
-        <v>0.5231162408413157</v>
+        <v>0.4421248145718281</v>
       </c>
       <c r="K10" s="4">
         <v>82.06680032716902</v>
@@ -3735,13 +3735,13 @@
         <v>7.331378299120235</v>
       </c>
       <c r="H11" s="4">
-        <v>0.4622794895000493</v>
+        <v>0.3836370249363751</v>
       </c>
       <c r="I11" s="4">
-        <v>0.3272888751742891</v>
+        <v>0.1989955217561527</v>
       </c>
       <c r="J11" s="4">
-        <v>0.4703828895980458</v>
+        <v>0.3850358474765397</v>
       </c>
       <c r="K11" s="4">
         <v>84.01629860155205</v>
@@ -3767,13 +3767,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>92.81524926686217</v>
+        <v>92.66862170087975</v>
       </c>
       <c r="C12" s="3">
         <v>0</v>
       </c>
       <c r="D12" s="3">
-        <v>7.184750733137831</v>
+        <v>7.331378299120235</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
@@ -3782,16 +3782,16 @@
         <v>0</v>
       </c>
       <c r="G12" s="3">
-        <v>7.184750733137831</v>
+        <v>7.331378299120235</v>
       </c>
       <c r="H12" s="4">
-        <v>0.4578420204313769</v>
+        <v>0.3755016726713737</v>
       </c>
       <c r="I12" s="4">
-        <v>0.3272002887336231</v>
+        <v>0.1937544180881645</v>
       </c>
       <c r="J12" s="4">
-        <v>0.4652216236335473</v>
+        <v>0.3792448169608886</v>
       </c>
       <c r="K12" s="4">
         <v>82.26270273505295</v>
@@ -3835,13 +3835,13 @@
         <v>7.331378299120235</v>
       </c>
       <c r="H13" s="4">
-        <v>0.427220555601768</v>
+        <v>0.3382058041739836</v>
       </c>
       <c r="I13" s="4">
-        <v>0.2902324719933548</v>
+        <v>0.149472082650094</v>
       </c>
       <c r="J13" s="4">
-        <v>0.435056077242237</v>
+        <v>0.339584498236462</v>
       </c>
       <c r="K13" s="4">
         <v>82.9750433897899</v>
@@ -3891,7 +3891,7 @@
         <v>0.01986255870956897</v>
       </c>
       <c r="J14" s="4">
-        <v>0.01949918339171959</v>
+        <v>0.01972883585741075</v>
       </c>
       <c r="K14" s="4">
         <v>98.13775510204081</v>
@@ -3935,13 +3935,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.02923115799377069</v>
+        <v>0.02712473190922804</v>
       </c>
       <c r="I15" s="4">
-        <v>0.02923115799377069</v>
+        <v>0.02712473190922804</v>
       </c>
       <c r="J15" s="4">
-        <v>0.03117607444244576</v>
+        <v>0.02977074643400505</v>
       </c>
       <c r="K15" s="4">
         <v>91.48809523809526</v>
@@ -3985,13 +3985,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.01802876236818553</v>
+        <v>0.01766552409120202</v>
       </c>
       <c r="I16" s="4">
-        <v>0.01802876236818553</v>
+        <v>0.01766552409120202</v>
       </c>
       <c r="J16" s="4">
-        <v>0.01874862504782006</v>
+        <v>0.01847653841562985</v>
       </c>
       <c r="K16" s="4">
         <v>98.41836734693878</v>
@@ -4035,13 +4035,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.03581291190950923</v>
+        <v>0.03366057925779872</v>
       </c>
       <c r="I17" s="4">
-        <v>0.03581291190950923</v>
+        <v>0.03366057925779872</v>
       </c>
       <c r="J17" s="4">
-        <v>0.04048272202358524</v>
+        <v>0.0437145961757374</v>
       </c>
       <c r="K17" s="4">
         <v>88.8095238095238</v>
@@ -5056,13 +5056,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C6" s="5">
         <v>12</v>
       </c>
       <c r="D6" s="5">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E6" s="5">
         <v>0</v>
@@ -5071,7 +5071,7 @@
         <v>30</v>
       </c>
       <c r="G6" s="5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -5188,13 +5188,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C9" s="5">
         <v>10</v>
       </c>
       <c r="D9" s="5">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E9" s="5">
         <v>0</v>
@@ -5203,7 +5203,7 @@
         <v>8</v>
       </c>
       <c r="G9" s="5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H9" s="5">
         <v>0</v>
@@ -5320,13 +5320,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C12" s="5">
         <v>0</v>
       </c>
       <c r="D12" s="5">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" s="5">
         <v>0</v>
@@ -5335,7 +5335,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="5">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H12" s="5">
         <v>0</v>
@@ -5738,16 +5738,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2491550111108355</v>
+        <v>-0.2350420463061553</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09153112491536536</v>
+        <v>0.08978756165039314</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09153112491536536</v>
+        <v>0.08978756165039314</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -5920,7 +5920,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3462827963961495</v>
+        <v>-0.3424988970312484</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
@@ -6102,16 +6102,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.07765869152628706</v>
+        <v>-0.07092100173101556</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.03985813784775378</v>
+        <v>0.03904723526549603</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.03985813784775378</v>
+        <v>0.03904723526549603</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -6284,16 +6284,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1809437421223123</v>
+        <v>-0.1677514915148919</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06949339269271088</v>
+        <v>0.06700050708008003</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07232433699843796</v>
+        <v>0.07197132438476501</v>
       </c>
       <c r="R3" s="5">
         <v>20</v>
@@ -6466,16 +6466,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1223952309952843</v>
+        <v>0.117628431462407</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.01543094200710667</v>
+        <v>0.01539169081868508</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.01543094200710667</v>
+        <v>0.01539169081868508</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
